--- a/DEV/org.openl.rules/test/rules/dt/SimpleDTRangeAndArray.xlsx
+++ b/DEV/org.openl.rules/test/rules/dt/SimpleDTRangeAndArray.xlsx
@@ -78,10 +78,10 @@
     <t>(-67; 123.00001]</t>
   </si>
   <si>
-    <t>(67.9M; 123.00001M]</t>
-  </si>
-  <si>
-    <t>($67.9; $123.00001]</t>
+    <t>(67900000; 123000010]</t>
+  </si>
+  <si>
+    <t>(67.9; 123.00001]</t>
   </si>
   <si>
     <t>10,15,20</t>
@@ -108,10 +108,10 @@
     <t>&lt; 200</t>
   </si>
   <si>
-    <t>[200 .. 1K]</t>
-  </si>
-  <si>
-    <t>&gt; 1K</t>
+    <t>[200 .. 1000]</t>
+  </si>
+  <si>
+    <t>&gt; 1000</t>
   </si>
   <si>
     <t>DE</t>
@@ -319,7 +319,7 @@
     <t>SimpleRules int TestArray2 ( String value)</t>
   </si>
   <si>
-    <t>200 .. 66M</t>
+    <t>200 .. 66000000</t>
   </si>
   <si>
     <t>150.005</t>
